--- a/InputData/hydgn/BHPSbP/BAU Hydrogen Production Shr by Pathway.xlsx
+++ b/InputData/hydgn/BHPSbP/BAU Hydrogen Production Shr by Pathway.xlsx
@@ -1,24 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10315"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipL\InputData\hydgn\BHPSbP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/hydgn/BHPSbP/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D55ED39-1A8E-2747-9B85-B38973393AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25815" windowHeight="11970"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BHPSbP" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -90,7 +102,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -427,19 +439,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.73046875" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -447,62 +459,62 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B4" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>0.02</v>
       </c>
@@ -510,7 +522,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>0.76</v>
       </c>
@@ -518,7 +530,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24">
         <f>0.22</f>
         <v>0.22</v>
@@ -529,8 +541,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1"/>
-    <hyperlink ref="B19" r:id="rId2"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B19" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
@@ -538,17 +550,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:BC6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.1328125" customWidth="1"/>
+    <col min="1" max="1" width="30.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -654,8 +666,68 @@
       <c r="AI1">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="AJ1">
+        <v>2051</v>
+      </c>
+      <c r="AK1">
+        <v>2052</v>
+      </c>
+      <c r="AL1">
+        <v>2053</v>
+      </c>
+      <c r="AM1">
+        <v>2054</v>
+      </c>
+      <c r="AN1">
+        <v>2055</v>
+      </c>
+      <c r="AO1">
+        <v>2056</v>
+      </c>
+      <c r="AP1">
+        <v>2057</v>
+      </c>
+      <c r="AQ1">
+        <v>2058</v>
+      </c>
+      <c r="AR1">
+        <v>2059</v>
+      </c>
+      <c r="AS1">
+        <v>2060</v>
+      </c>
+      <c r="AT1">
+        <v>2061</v>
+      </c>
+      <c r="AU1">
+        <v>2062</v>
+      </c>
+      <c r="AV1">
+        <v>2063</v>
+      </c>
+      <c r="AW1">
+        <v>2064</v>
+      </c>
+      <c r="AX1">
+        <v>2065</v>
+      </c>
+      <c r="AY1">
+        <v>2066</v>
+      </c>
+      <c r="AZ1">
+        <v>2067</v>
+      </c>
+      <c r="BA1">
+        <v>2068</v>
+      </c>
+      <c r="BB1">
+        <v>2069</v>
+      </c>
+      <c r="BC1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -794,8 +866,88 @@
         <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="AJ2">
+        <f>AI2</f>
+        <v>0.05</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" ref="AK2:BC6" si="1">AJ2</f>
+        <v>0.05</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="BA2">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="BB2">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="BC2">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -803,67 +955,67 @@
         <v>0.95</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:R6" si="1">$B3</f>
+        <f t="shared" ref="C3:R6" si="2">$B3</f>
         <v>0.95</v>
       </c>
       <c r="D3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
       <c r="E3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
       <c r="F3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
       <c r="G3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
       <c r="H3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
       <c r="I3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
       <c r="J3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
       <c r="K3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
       <c r="L3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
       <c r="M3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
       <c r="N3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
       <c r="O3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
       <c r="P3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
       <c r="Q3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
       <c r="R3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
       <c r="S3">
@@ -934,8 +1086,88 @@
         <f t="shared" si="0"/>
         <v>0.95</v>
       </c>
-    </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="AJ3">
+        <f t="shared" ref="AJ3:AY6" si="3">AI3</f>
+        <v>0.95</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="3"/>
+        <v>0.95</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="3"/>
+        <v>0.95</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="3"/>
+        <v>0.95</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="3"/>
+        <v>0.95</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="3"/>
+        <v>0.95</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="3"/>
+        <v>0.95</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="3"/>
+        <v>0.95</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="3"/>
+        <v>0.95</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="3"/>
+        <v>0.95</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="3"/>
+        <v>0.95</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="3"/>
+        <v>0.95</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="3"/>
+        <v>0.95</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="3"/>
+        <v>0.95</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="3"/>
+        <v>0.95</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="3"/>
+        <v>0.95</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="1"/>
+        <v>0.95</v>
+      </c>
+      <c r="BA3">
+        <f t="shared" si="1"/>
+        <v>0.95</v>
+      </c>
+      <c r="BB3">
+        <f t="shared" si="1"/>
+        <v>0.95</v>
+      </c>
+      <c r="BC3">
+        <f t="shared" si="1"/>
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -943,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D4">
@@ -1074,8 +1306,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="AJ4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1083,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D5">
@@ -1214,8 +1526,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="AJ5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1223,7 +1615,7 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D6">
@@ -1352,6 +1744,86 @@
       </c>
       <c r="AI6">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
